--- a/research/traditional_assets/database/data/peru/peru_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_brokerage_investment_banking.xlsx
@@ -587,47 +587,29 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.09390000000000001</v>
-      </c>
       <c r="E2">
-        <v>0.266</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="K2">
-        <v>11.9</v>
-      </c>
-      <c r="L2">
-        <v>0.0268018018018018</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
-        <v>9.57</v>
+        <v>7.19</v>
       </c>
       <c r="N2">
-        <v>0.1434782608695652</v>
+        <v>0.1190397350993378</v>
       </c>
       <c r="O2">
-        <v>0.8042016806722689</v>
+        <v>5.706349206349207</v>
       </c>
       <c r="P2">
-        <v>9.57</v>
+        <v>7.19</v>
       </c>
       <c r="Q2">
-        <v>0.1434782608695652</v>
+        <v>0.1190397350993378</v>
       </c>
       <c r="R2">
-        <v>0.8042016806722689</v>
+        <v>5.706349206349207</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +618,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.5</v>
+        <v>12.3</v>
       </c>
       <c r="V2">
-        <v>0.2173913043478261</v>
+        <v>0.2036423841059603</v>
       </c>
       <c r="W2">
-        <v>0.3979933110367893</v>
+        <v>0.04436619718309859</v>
       </c>
       <c r="X2">
-        <v>0.04399675783972171</v>
+        <v>0.08910103789316</v>
       </c>
       <c r="Y2">
-        <v>0.3539965531970676</v>
+        <v>-0.0447348407100614</v>
       </c>
       <c r="Z2">
-        <v>13.54897772352762</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04190939304310892</v>
+        <v>0.07745489037722314</v>
       </c>
       <c r="AC2">
-        <v>-0.04190939304310892</v>
+        <v>-0.07745489037722314</v>
       </c>
       <c r="AD2">
-        <v>13.3</v>
+        <v>23.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.3</v>
+        <v>23.2</v>
       </c>
       <c r="AG2">
-        <v>-1.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="AH2">
-        <v>0.16625</v>
+        <v>0.277511961722488</v>
       </c>
       <c r="AI2">
-        <v>0.3189448441247003</v>
+        <v>0.4936170212765957</v>
       </c>
       <c r="AJ2">
-        <v>-0.01832061068702289</v>
+        <v>0.152875175315568</v>
       </c>
       <c r="AK2">
-        <v>-0.0441176470588235</v>
+        <v>0.3141210374639769</v>
       </c>
       <c r="AL2">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.037</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +694,29 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.09390000000000001</v>
-      </c>
       <c r="E3">
-        <v>0.266</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="K3">
-        <v>11.9</v>
-      </c>
-      <c r="L3">
-        <v>0.0268018018018018</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
-        <v>9.57</v>
+        <v>7.19</v>
       </c>
       <c r="N3">
-        <v>0.1434782608695652</v>
+        <v>0.1190397350993378</v>
       </c>
       <c r="O3">
-        <v>0.8042016806722689</v>
+        <v>5.706349206349207</v>
       </c>
       <c r="P3">
-        <v>9.57</v>
+        <v>7.19</v>
       </c>
       <c r="Q3">
-        <v>0.1434782608695652</v>
+        <v>0.1190397350993378</v>
       </c>
       <c r="R3">
-        <v>0.8042016806722689</v>
+        <v>5.706349206349207</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +725,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.5</v>
+        <v>12.3</v>
       </c>
       <c r="V3">
-        <v>0.2173913043478261</v>
+        <v>0.2036423841059603</v>
       </c>
       <c r="W3">
-        <v>0.3979933110367893</v>
+        <v>0.04436619718309859</v>
       </c>
       <c r="X3">
-        <v>0.04399675783972171</v>
+        <v>0.08910103789316</v>
       </c>
       <c r="Y3">
-        <v>0.3539965531970676</v>
+        <v>-0.0447348407100614</v>
       </c>
       <c r="Z3">
-        <v>13.54897772352762</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04190939304310892</v>
+        <v>0.07745489037722314</v>
       </c>
       <c r="AC3">
-        <v>-0.04190939304310892</v>
+        <v>-0.07745489037722314</v>
       </c>
       <c r="AD3">
-        <v>13.3</v>
+        <v>23.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.3</v>
+        <v>23.2</v>
       </c>
       <c r="AG3">
-        <v>-1.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="AH3">
-        <v>0.16625</v>
+        <v>0.277511961722488</v>
       </c>
       <c r="AI3">
-        <v>0.3189448441247003</v>
+        <v>0.4936170212765957</v>
       </c>
       <c r="AJ3">
-        <v>-0.01832061068702289</v>
+        <v>0.152875175315568</v>
       </c>
       <c r="AK3">
-        <v>-0.0441176470588235</v>
+        <v>0.3141210374639769</v>
       </c>
       <c r="AL3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.037</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
